--- a/4_results/e_QA/Results_vs_Smither_photons.xlsx
+++ b/4_results/e_QA/Results_vs_Smither_photons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-26.04\home\clarence\Geant4_SAF_Calculations\PHITS_Geant4_python_scripts\4_results\e_QA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996A2DC6-1E0F-442D-92C5-0FCFED2C2EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED4D682-E4E4-412C-A8AE-D581369C8268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{727AC7D9-CB15-476D-9018-9B172206195C}"/>
   </bookViews>
@@ -45,9 +45,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="18">
   <si>
     <t>Photon Energy (MeV)</t>
-  </si>
-  <si>
-    <t>Results vs Annex I of ICRP 145</t>
   </si>
   <si>
     <t>Source: Cortical Bone</t>
@@ -97,6 +94,9 @@
   <si>
     <t>Photon</t>
   </si>
+  <si>
+    <t>Results vs Smither et al. 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -104,7 +104,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000E+00"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -148,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -173,17 +173,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -193,9 +189,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -548,7 +541,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -556,7 +549,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -570,7 +563,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -578,19 +571,19 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="1"/>
       <c r="F5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="1"/>
       <c r="K5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -598,19 +591,19 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="1"/>
       <c r="F6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="1"/>
       <c r="K6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -621,37 +614,37 @@
         <v>0</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F7" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="K7" s="1" t="s">
         <v>0</v>
       </c>
       <c r="L7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -827,19 +820,19 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -847,19 +840,19 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -870,37 +863,37 @@
         <v>0</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="K15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="L15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1074,19 +1067,19 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -1094,19 +1087,19 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -1117,37 +1110,37 @@
         <v>0</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F23" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="K23" s="1" t="s">
         <v>0</v>
       </c>
       <c r="L23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N23" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1322,19 +1315,19 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="1"/>
       <c r="K29" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -1342,19 +1335,19 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="1"/>
       <c r="K30" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -1365,37 +1358,37 @@
         <v>0</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F31" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G31" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H31" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="K31" s="1" t="s">
         <v>0</v>
       </c>
       <c r="L31" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N31" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="M31" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -1574,27 +1567,27 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" style="18"/>
+    <col min="2" max="2" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="13"/>
     <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="18"/>
+    <col min="7" max="7" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="13"/>
     <col min="11" max="11" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9" style="18" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -1602,106 +1595,106 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>6</v>
-      </c>
       <c r="F7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>6</v>
-      </c>
       <c r="K7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="13" t="s">
         <v>5</v>
-      </c>
-      <c r="M7" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="N7" s="18" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>0.01</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="10">
         <v>9.0859711106377605E-7</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="11">
         <v>9.7189999999999996E-7</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="12">
         <f>((B8-C8)/C8)*100</f>
         <v>-6.5133129886021113</v>
       </c>
       <c r="F8" s="1">
         <v>0.01</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="10">
         <v>1.1300915751383E-3</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="11">
         <v>1.119E-3</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="12">
         <f t="shared" ref="I8:I10" si="0">((G8-H8)/H8)*100</f>
         <v>0.99120421253798174</v>
       </c>
       <c r="K8" s="1">
         <v>0.01</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="10">
         <v>3.1955318349879002E-3</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="11">
         <v>3.1700000000000001E-3</v>
       </c>
-      <c r="N8" s="14">
+      <c r="N8" s="12">
         <f>((L8-M8)/M8)*100</f>
         <v>0.80542066207886687</v>
       </c>
@@ -1710,39 +1703,39 @@
       <c r="A9" s="1">
         <v>0.1</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="10">
         <v>6.4666327092130996E-3</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="11">
         <v>6.4270000000000004E-3</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="12">
         <f>((B9-C9)/C9)*100</f>
         <v>0.61665954898240571</v>
       </c>
       <c r="F9" s="1">
         <v>0.1</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="10">
         <v>1.22370037261481E-2</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="11">
         <v>1.2239999999999999E-2</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="12">
         <f t="shared" si="0"/>
         <v>-2.4479361535125751E-2</v>
       </c>
       <c r="K9" s="1">
         <v>0.1</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="10">
         <v>1.5131640319310699E-2</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="11">
         <v>1.5140000000000001E-2</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="12">
         <f t="shared" ref="N9:N10" si="1">((L9-M9)/M9)*100</f>
         <v>-5.5215856600404546E-2</v>
       </c>
@@ -1751,39 +1744,39 @@
       <c r="A10" s="1">
         <v>1</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="10">
         <v>5.8332812357237002E-3</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="11">
         <v>5.9049999999999997E-3</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="12">
         <f>((B10-C10)/C10)*100</f>
         <v>-1.2145430021388568</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="10">
         <v>9.7044632833146998E-3</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="11">
         <v>9.7079999999999996E-3</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="12">
         <f t="shared" si="0"/>
         <v>-3.6430950610834491E-2</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="10">
         <v>1.1726599926934001E-2</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="11">
         <v>1.175E-2</v>
       </c>
-      <c r="N10" s="14">
+      <c r="N10" s="12">
         <f t="shared" si="1"/>
         <v>-0.1991495580085042</v>
       </c>
@@ -1792,169 +1785,169 @@
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="10">
         <v>3.525409833135E-3</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="11">
         <v>3.6089999999999998E-3</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="12">
         <f>((B11-C11)/C11)*100</f>
         <v>-2.316158682876138</v>
       </c>
       <c r="F11" s="1">
         <v>10</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="10">
         <v>5.4900523799021996E-3</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="11">
         <v>5.5129999999999997E-3</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="12">
         <f>((G11-H11)/H11)*100</f>
         <v>-0.41624560307999442</v>
       </c>
       <c r="K11" s="1">
         <v>10</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="10">
         <v>6.3738672863258997E-3</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="11">
         <v>6.4120000000000002E-3</v>
       </c>
-      <c r="N11" s="14">
+      <c r="N11" s="12">
         <f>((L11-M11)/M11)*100</f>
         <v>-0.59470857258422438</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="14"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="14"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="14"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="12"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="12"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="12"/>
       <c r="F13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="12"/>
       <c r="K13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="12"/>
+      <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="14"/>
-      <c r="F14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="14"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="12"/>
       <c r="K14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>6</v>
-      </c>
       <c r="F15" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>6</v>
-      </c>
       <c r="K15" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L15" s="12" t="s">
+      <c r="L15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" s="12" t="s">
         <v>5</v>
-      </c>
-      <c r="M15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="N15" s="14" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>0.01</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="10">
         <v>2.9128450235686501E-7</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="11">
         <v>3.0820000000000002E-7</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="12">
         <f>((B16-C16)/C16)*100</f>
         <v>-5.4884807407965637</v>
       </c>
       <c r="F16" s="1">
         <v>0.01</v>
       </c>
-      <c r="G16" s="12">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13">
-        <v>0</v>
-      </c>
-      <c r="I16" s="14">
+      <c r="G16" s="10">
+        <v>0</v>
+      </c>
+      <c r="H16" s="11">
+        <v>0</v>
+      </c>
+      <c r="I16" s="12">
         <f>IFERROR((((G16-H16)/H16)*100), 0)</f>
         <v>0</v>
       </c>
       <c r="K16" s="1">
         <v>0.01</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="10">
         <v>3.0640746825640898E-5</v>
       </c>
-      <c r="M16" s="13">
+      <c r="M16" s="11">
         <v>3.0130000000000001E-5</v>
       </c>
-      <c r="N16" s="14">
+      <c r="N16" s="12">
         <f t="shared" ref="N16:N18" si="2">((L16-M16)/M16)*100</f>
         <v>1.6951437956883413</v>
       </c>
@@ -1963,39 +1956,39 @@
       <c r="A17" s="1">
         <v>0.1</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="10">
         <v>3.2905121218036E-3</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="11">
         <v>3.2729999999999999E-3</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="12">
         <f>((B17-C17)/C17)*100</f>
         <v>0.53504802333028112</v>
       </c>
       <c r="F17" s="1">
         <v>0.1</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="10">
         <v>8.2306218990838302E-5</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="11">
         <v>8.1409999999999995E-5</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="12">
         <f t="shared" ref="I17:I18" si="3">((G17-H17)/H17)*100</f>
         <v>1.1008708891270205</v>
       </c>
       <c r="K17" s="1">
         <v>0.1</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="10">
         <v>2.0536807159182002E-3</v>
       </c>
-      <c r="M17" s="13">
+      <c r="M17" s="11">
         <v>2.0739999999999999E-3</v>
       </c>
-      <c r="N17" s="14">
+      <c r="N17" s="12">
         <f t="shared" si="2"/>
         <v>-0.97971475804241714</v>
       </c>
@@ -2004,39 +1997,39 @@
       <c r="A18" s="1">
         <v>1</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="10">
         <v>2.2415973330099002E-3</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="11">
         <v>2.2750000000000001E-3</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="12">
         <f>((B18-C18)/C18)*100</f>
         <v>-1.468249098465932</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="10">
         <v>3.012746339927E-4</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="11">
         <v>3.054E-4</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="12">
         <f t="shared" si="3"/>
         <v>-1.3508074680091664</v>
       </c>
       <c r="K18" s="1">
         <v>1</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="10">
         <v>2.0172463310244998E-3</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="11">
         <v>2.016E-3</v>
       </c>
-      <c r="N18" s="14">
+      <c r="N18" s="12">
         <f t="shared" si="2"/>
         <v>6.1821975421616958E-2</v>
       </c>
@@ -2045,169 +2038,169 @@
       <c r="A19" s="1">
         <v>10</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="10">
         <v>1.4301637256376001E-3</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="11">
         <v>1.464E-3</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="12">
         <f>((B19-C19)/C19)*100</f>
         <v>-2.3112209263934402</v>
       </c>
       <c r="F19" s="1">
         <v>10</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="10">
         <v>3.7509955178870001E-4</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="11">
         <v>3.7599999999999998E-4</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="12">
         <f>((G19-H19)/H19)*100</f>
         <v>-0.23948090726062907</v>
       </c>
       <c r="K19" s="1">
         <v>10</v>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="10">
         <v>1.3475553635732E-3</v>
       </c>
-      <c r="M19" s="13">
+      <c r="M19" s="11">
         <v>1.351E-3</v>
       </c>
-      <c r="N19" s="14">
+      <c r="N19" s="12">
         <f>((L19-M19)/M19)*100</f>
         <v>-0.25496938762397842</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="14"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="14"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="14"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="12"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="12"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="12"/>
       <c r="F21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="12"/>
       <c r="K21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="14"/>
+        <v>3</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="12"/>
       <c r="F22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="12"/>
+      <c r="K22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="14"/>
-      <c r="K22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="14"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="12"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>6</v>
-      </c>
       <c r="F23" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H23" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>6</v>
-      </c>
       <c r="K23" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L23" s="12" t="s">
+      <c r="L23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N23" s="12" t="s">
         <v>5</v>
-      </c>
-      <c r="M23" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="N23" s="14" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>0.01</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="10">
         <v>2.7814538498098599E-5</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="14">
         <v>3.0349999999999999E-5</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="12">
         <f>((B24-C24)/C24)*100</f>
         <v>-8.35407414135552</v>
       </c>
       <c r="F24" s="1">
         <v>0.01</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="10">
         <v>1.472473556929E-4</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="14">
         <v>1.4569999999999999E-4</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="12">
         <f t="shared" ref="I24:I26" si="4">((G24-H24)/H24)*100</f>
         <v>1.0620148887440015</v>
       </c>
       <c r="K24" s="1">
         <v>0.01</v>
       </c>
-      <c r="L24" s="12">
+      <c r="L24" s="10">
         <v>3.9619855973331E-3</v>
       </c>
-      <c r="M24" s="16">
+      <c r="M24" s="14">
         <v>3.9280000000000001E-3</v>
       </c>
-      <c r="N24" s="14">
+      <c r="N24" s="12">
         <f t="shared" ref="N24:N26" si="5">((L24-M24)/M24)*100</f>
         <v>0.865213781392564</v>
       </c>
@@ -2216,39 +2209,39 @@
       <c r="A25" s="1">
         <v>0.1</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="10">
         <v>8.4616244395612009E-3</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="14">
         <v>8.4150000000000006E-3</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="12">
         <f>((B25-C25)/C25)*100</f>
         <v>0.55406345289602199</v>
       </c>
       <c r="F25" s="1">
         <v>0.1</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="10">
         <v>4.3946306367627997E-3</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="14">
         <v>4.4640000000000001E-3</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="12">
         <f t="shared" si="4"/>
         <v>-1.5539731907975003</v>
       </c>
       <c r="K25" s="1">
         <v>0.1</v>
       </c>
-      <c r="L25" s="12">
+      <c r="L25" s="10">
         <v>1.6543527315983901E-2</v>
       </c>
-      <c r="M25" s="16">
+      <c r="M25" s="14">
         <v>1.6549999999999999E-2</v>
       </c>
-      <c r="N25" s="14">
+      <c r="N25" s="12">
         <f t="shared" si="5"/>
         <v>-3.9109873209049295E-2</v>
       </c>
@@ -2257,39 +2250,39 @@
       <c r="A26" s="1">
         <v>1</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="10">
         <v>7.6412068026594001E-3</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="14">
         <v>7.7460000000000003E-3</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="12">
         <f>((B26-C26)/C26)*100</f>
         <v>-1.3528685429976786</v>
       </c>
       <c r="F26" s="1">
         <v>1</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="10">
         <v>4.2781349576272E-3</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="14">
         <v>4.261E-3</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="12">
         <f t="shared" si="4"/>
         <v>0.40213465447547536</v>
       </c>
       <c r="K26" s="1">
         <v>1</v>
       </c>
-      <c r="L26" s="12">
+      <c r="L26" s="10">
         <v>1.3051074979061E-2</v>
       </c>
-      <c r="M26" s="16">
+      <c r="M26" s="14">
         <v>1.3100000000000001E-2</v>
       </c>
-      <c r="N26" s="14">
+      <c r="N26" s="12">
         <f t="shared" si="5"/>
         <v>-0.37347344228244689</v>
       </c>
@@ -2298,169 +2291,169 @@
       <c r="A27" s="1">
         <v>10</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="10">
         <v>4.5377813766396E-3</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="14">
         <v>4.6509999999999998E-3</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="12">
         <f>((B27-C27)/C27)*100</f>
         <v>-2.4342856022446737</v>
       </c>
       <c r="F27" s="1">
         <v>10</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="10">
         <v>2.7905703573008001E-3</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="14">
         <v>2.797E-3</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="12">
         <f>((G27-H27)/H27)*100</f>
         <v>-0.22987639253485592</v>
       </c>
       <c r="K27" s="1">
         <v>10</v>
       </c>
-      <c r="L27" s="12">
+      <c r="L27" s="10">
         <v>7.0511911871362996E-3</v>
       </c>
-      <c r="M27" s="16">
+      <c r="M27" s="14">
         <v>7.0920000000000002E-3</v>
       </c>
-      <c r="N27" s="14">
+      <c r="N27" s="12">
         <f>((L27-M27)/M27)*100</f>
         <v>-0.57542037314862726</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="14"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="14"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="14"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="12"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="12"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="12"/>
       <c r="F29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="12"/>
       <c r="K29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="12"/>
+      <c r="F30" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="14"/>
-      <c r="F30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="14"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="12"/>
       <c r="K30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="12"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>6</v>
-      </c>
       <c r="F31" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G31" s="12" t="s">
+      <c r="G31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H31" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" s="14" t="s">
-        <v>6</v>
-      </c>
       <c r="K31" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L31" s="12" t="s">
+      <c r="L31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N31" s="12" t="s">
         <v>5</v>
-      </c>
-      <c r="M31" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="N31" s="14" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>0.01</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="10">
         <v>9.2021645271622707E-6</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="14">
         <v>1.0210000000000001E-5</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="12">
         <f>((B32-C32)/C32)*100</f>
         <v>-9.8710624176075381</v>
       </c>
       <c r="F32" s="1">
         <v>0.01</v>
       </c>
-      <c r="G32" s="12">
-        <v>0</v>
-      </c>
-      <c r="H32" s="16">
-        <v>0</v>
-      </c>
-      <c r="I32" s="14">
+      <c r="G32" s="10">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>0</v>
+      </c>
+      <c r="I32" s="12">
         <f>IFERROR((((G32-H32)/H32)*100), 0)</f>
         <v>0</v>
       </c>
       <c r="K32" s="1">
         <v>0.01</v>
       </c>
-      <c r="L32" s="12">
+      <c r="L32" s="10">
         <v>7.5377314516415496E-5</v>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="14">
         <v>7.4469999999999997E-5</v>
       </c>
-      <c r="N32" s="14">
+      <c r="N32" s="12">
         <f t="shared" ref="N32:N34" si="6">((L32-M32)/M32)*100</f>
         <v>1.2183624498663876</v>
       </c>
@@ -2469,39 +2462,39 @@
       <c r="A33" s="1">
         <v>0.1</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="10">
         <v>4.3576067516188999E-3</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="14">
         <v>4.3569999999999998E-3</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="12">
         <f>((B33-C33)/C33)*100</f>
         <v>1.3925903578153523E-2</v>
       </c>
       <c r="F33" s="1">
         <v>0.1</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="10">
         <v>1.097520653893E-4</v>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="14">
         <v>1.0900000000000001E-4</v>
       </c>
-      <c r="I33" s="14">
+      <c r="I33" s="12">
         <f t="shared" ref="I33:I34" si="7">((G33-H33)/H33)*100</f>
         <v>0.68996824706421556</v>
       </c>
       <c r="K33" s="1">
         <v>0.1</v>
       </c>
-      <c r="L33" s="12">
+      <c r="L33" s="10">
         <v>2.2442447109375999E-3</v>
       </c>
-      <c r="M33" s="16">
+      <c r="M33" s="14">
         <v>2.2720000000000001E-3</v>
       </c>
-      <c r="N33" s="14">
+      <c r="N33" s="12">
         <f t="shared" si="6"/>
         <v>-1.2216236383098715</v>
       </c>
@@ -2510,39 +2503,39 @@
       <c r="A34" s="1">
         <v>1</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="10">
         <v>2.9836726761977E-3</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="14">
         <v>3.0439999999999998E-3</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="12">
         <f>((B34-C34)/C34)*100</f>
         <v>-1.9818437517181291</v>
       </c>
       <c r="F34" s="1">
         <v>1</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="10">
         <v>3.7570414823559999E-4</v>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="14">
         <v>3.7800000000000003E-4</v>
       </c>
-      <c r="I34" s="14">
+      <c r="I34" s="12">
         <f t="shared" si="7"/>
         <v>-0.60736819164022138</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
-      <c r="L34" s="12">
+      <c r="L34" s="10">
         <v>2.2108796687601998E-3</v>
       </c>
-      <c r="M34" s="16">
+      <c r="M34" s="14">
         <v>2.2109999999999999E-3</v>
       </c>
-      <c r="N34" s="14">
+      <c r="N34" s="12">
         <f t="shared" si="6"/>
         <v>-5.4423898597949581E-3</v>
       </c>
@@ -2551,39 +2544,39 @@
       <c r="A35" s="1">
         <v>10</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="10">
         <v>1.8640677402742001E-3</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="14">
         <v>1.916E-3</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="12">
         <f>((B35-C35)/C35)*100</f>
         <v>-2.7104519689874671</v>
       </c>
       <c r="F35" s="1">
         <v>10</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="10">
         <v>4.4010351295630001E-4</v>
       </c>
-      <c r="H35" s="16">
+      <c r="H35" s="14">
         <v>4.417E-4</v>
       </c>
-      <c r="I35" s="14">
+      <c r="I35" s="12">
         <f>((G35-H35)/H35)*100</f>
         <v>-0.36144148600860243</v>
       </c>
       <c r="K35" s="1">
         <v>10</v>
       </c>
-      <c r="L35" s="12">
+      <c r="L35" s="10">
         <v>1.4551181908267999E-3</v>
       </c>
-      <c r="M35" s="16">
+      <c r="M35" s="14">
         <v>1.4599999999999999E-3</v>
       </c>
-      <c r="N35" s="14">
+      <c r="N35" s="12">
         <f>((L35-M35)/M35)*100</f>
         <v>-0.33437049131506841</v>
       </c>
@@ -2609,7 +2602,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2617,7 +2610,7 @@
     </row>
     <row r="2" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2631,7 +2624,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -2639,19 +2632,19 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="F5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="K5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -2659,19 +2652,19 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="F6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="K6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -2682,37 +2675,37 @@
         <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F7" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="K7" s="1" t="s">
         <v>0</v>
       </c>
       <c r="L7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -2890,19 +2883,19 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -2910,19 +2903,19 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -2933,37 +2926,37 @@
         <v>0</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="K15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="L15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -3137,19 +3130,19 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -3157,19 +3150,19 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -3180,37 +3173,37 @@
         <v>0</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F23" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="K23" s="1" t="s">
         <v>0</v>
       </c>
       <c r="L23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N23" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -3388,19 +3381,19 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -3408,19 +3401,19 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -3431,37 +3424,37 @@
         <v>0</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F31" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H31" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="K31" s="1" t="s">
         <v>0</v>
       </c>
       <c r="L31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N31" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="M31" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -3694,162 +3687,162 @@
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="10"/>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="10"/>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="10"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="10"/>
+      <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="10"/>
+      <c r="D5" s="1"/>
       <c r="F5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="10"/>
+      <c r="I5" s="1"/>
       <c r="K5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="10"/>
+      <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="10"/>
+      <c r="D6" s="1"/>
       <c r="F6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="10"/>
+      <c r="I6" s="1"/>
       <c r="K6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="10"/>
+      <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>6</v>
-      </c>
       <c r="F7" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>6</v>
-      </c>
       <c r="K7" s="1" t="s">
         <v>0</v>
       </c>
       <c r="L7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>0.01</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="10">
         <v>6.6877249495831396E-8</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="11">
         <v>7.1680000000000004E-8</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="12">
         <f t="shared" ref="D8:D10" si="0">((B8-C8)/C8)*100</f>
         <v>-6.7002657703245081</v>
       </c>
       <c r="F8" s="1">
         <v>0.01</v>
       </c>
-      <c r="G8" s="12">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13">
-        <v>0</v>
-      </c>
-      <c r="I8" s="14">
+      <c r="G8" s="10">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12">
         <f>IFERROR((((G8-H8)/H8)*100), 0)</f>
         <v>0</v>
       </c>
       <c r="K8" s="1">
         <v>0.01</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="10">
         <v>3.7818802999608398E-7</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="11">
         <v>3.5909999999999998E-7</v>
       </c>
-      <c r="N8" s="14">
+      <c r="N8" s="12">
         <f t="shared" ref="N8:N10" si="1">((L8-M8)/M8)*100</f>
         <v>5.3155193528499041</v>
       </c>
@@ -3858,39 +3851,39 @@
       <c r="A9" s="1">
         <v>0.1</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="10">
         <v>8.7565112842295997E-3</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="11">
         <v>8.7039999999999999E-3</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="12">
         <f t="shared" si="0"/>
         <v>0.60330060006433595</v>
       </c>
       <c r="F9" s="1">
         <v>0.1</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="10">
         <v>3.2388033123459999E-4</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="11">
         <v>3.19E-4</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="12">
         <f t="shared" ref="I9:I10" si="2">((G9-H9)/H9)*100</f>
         <v>1.5298843995611255</v>
       </c>
       <c r="K9" s="1">
         <v>0.1</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="10">
         <v>1.59614707262399E-2</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="11">
         <v>1.6140000000000002E-2</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="12">
         <f t="shared" si="1"/>
         <v>-1.1061293293686592</v>
       </c>
@@ -3899,39 +3892,39 @@
       <c r="A10" s="1">
         <v>1</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="10">
         <v>8.0253595571212998E-3</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="11">
         <v>8.1589999999999996E-3</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="12">
         <f t="shared" si="0"/>
         <v>-1.6379512547947033</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="10">
         <v>6.0873360793750001E-4</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="11">
         <v>6.0849999999999999E-4</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="12">
         <f t="shared" si="2"/>
         <v>3.839078677075098E-2</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="10">
         <v>1.2996270712615899E-2</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="11">
         <v>1.306E-2</v>
       </c>
-      <c r="N10" s="14">
+      <c r="N10" s="12">
         <f t="shared" si="1"/>
         <v>-0.48797310401302535</v>
       </c>
@@ -3940,169 +3933,169 @@
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="10">
         <v>4.6919085219553E-3</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="11">
         <v>4.8139999999999997E-3</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="12">
         <f>((B11-C11)/C11)*100</f>
         <v>-2.5361752813606087</v>
       </c>
       <c r="F11" s="1">
         <v>10</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="10">
         <v>6.0149263356060005E-4</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="11">
         <v>5.9460000000000003E-4</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="12">
         <f>((G11-H11)/H11)*100</f>
         <v>1.1592051060544939</v>
       </c>
       <c r="K11" s="1">
         <v>10</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="10">
         <v>7.3377414044156E-3</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="11">
         <v>7.3829999999999998E-3</v>
       </c>
-      <c r="N11" s="14">
+      <c r="N11" s="12">
         <f>((L11-M11)/M11)*100</f>
         <v>-0.61301091134226993</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="14"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="14"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="14"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="12"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="12"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="12"/>
       <c r="F13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="12"/>
       <c r="K13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="12"/>
+      <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="14"/>
-      <c r="F14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="14"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="12"/>
       <c r="K14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>6</v>
-      </c>
       <c r="F15" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>6</v>
-      </c>
       <c r="K15" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L15" s="12" t="s">
+      <c r="L15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" s="12" t="s">
         <v>5</v>
-      </c>
-      <c r="M15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="N15" s="14" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>0.01</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="10">
         <v>3.4268434008083903E-8</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="11">
         <v>3.6739999999999997E-8</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="12">
         <f t="shared" ref="D16:D18" si="3">((B16-C16)/C16)*100</f>
         <v>-6.7271801630813668</v>
       </c>
       <c r="F16" s="1">
         <v>0.01</v>
       </c>
-      <c r="G16" s="12">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13">
-        <v>0</v>
-      </c>
-      <c r="I16" s="14">
+      <c r="G16" s="10">
+        <v>0</v>
+      </c>
+      <c r="H16" s="11">
+        <v>0</v>
+      </c>
+      <c r="I16" s="12">
         <f>IFERROR((((G16-H16)/H16)*100), 0)</f>
         <v>0</v>
       </c>
       <c r="K16" s="1">
         <v>0.01</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="10">
         <v>1.6951655925556001E-3</v>
       </c>
-      <c r="M16" s="13">
+      <c r="M16" s="11">
         <v>1.676E-3</v>
       </c>
-      <c r="N16" s="14">
+      <c r="N16" s="12">
         <f t="shared" ref="N16:N18" si="4">((L16-M16)/M16)*100</f>
         <v>1.1435317753938006</v>
       </c>
@@ -4111,39 +4104,39 @@
       <c r="A17" s="1">
         <v>0.1</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="10">
         <v>5.2898428734127001E-3</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="11">
         <v>5.2820000000000002E-3</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="12">
         <f t="shared" si="3"/>
         <v>0.14848302560961557</v>
       </c>
       <c r="F17" s="1">
         <v>0.1</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="10">
         <v>1.8071902863615E-3</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="11">
         <v>1.789E-3</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="12">
         <f t="shared" ref="I17:I18" si="5">((G17-H17)/H17)*100</f>
         <v>1.0167851515651207</v>
       </c>
       <c r="K17" s="1">
         <v>0.1</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="10">
         <v>3.7753036082117E-3</v>
       </c>
-      <c r="M17" s="13">
+      <c r="M17" s="11">
         <v>3.787E-3</v>
       </c>
-      <c r="N17" s="14">
+      <c r="N17" s="12">
         <f t="shared" si="4"/>
         <v>-0.30885639789543162</v>
       </c>
@@ -4152,39 +4145,39 @@
       <c r="A18" s="1">
         <v>1</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="10">
         <v>3.7011902924128002E-3</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="11">
         <v>3.7959999999999999E-3</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="12">
         <f t="shared" si="3"/>
         <v>-2.4976213800632174</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="10">
         <v>2.9160491227087E-3</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="11">
         <v>2.9320000000000001E-3</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="12">
         <f t="shared" si="5"/>
         <v>-0.54402719274557254</v>
       </c>
       <c r="K18" s="1">
         <v>1</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="10">
         <v>3.6408205447507002E-3</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="11">
         <v>3.6459999999999999E-3</v>
       </c>
-      <c r="N18" s="14">
+      <c r="N18" s="12">
         <f t="shared" si="4"/>
         <v>-0.14205856416071724</v>
       </c>
@@ -4193,169 +4186,169 @@
       <c r="A19" s="1">
         <v>10</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="10">
         <v>2.2585533639903001E-3</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="11">
         <v>2.3249999999999998E-3</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="12">
         <f>((B19-C19)/C19)*100</f>
         <v>-2.857919828374182</v>
       </c>
       <c r="F19" s="1">
         <v>10</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="10">
         <v>2.2425714048955E-3</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="11">
         <v>2.245E-3</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="12">
         <f>((G19-H19)/H19)*100</f>
         <v>-0.10817795565701703</v>
       </c>
       <c r="K19" s="1">
         <v>10</v>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="10">
         <v>1.9734734019313002E-3</v>
       </c>
-      <c r="M19" s="13">
+      <c r="M19" s="11">
         <v>1.98E-3</v>
       </c>
-      <c r="N19" s="14">
+      <c r="N19" s="12">
         <f>((L19-M19)/M19)*100</f>
         <v>-0.3296261650858478</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="14"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="14"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="14"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="12"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="12"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="12"/>
       <c r="F21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="12"/>
       <c r="K21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="14"/>
+        <v>3</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="12"/>
       <c r="F22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="12"/>
+      <c r="K22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="14"/>
-      <c r="K22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="14"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="12"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>6</v>
-      </c>
       <c r="F23" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H23" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>6</v>
-      </c>
       <c r="K23" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L23" s="12" t="s">
+      <c r="L23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N23" s="12" t="s">
         <v>5</v>
-      </c>
-      <c r="M23" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="N23" s="14" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>0.01</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="10">
         <v>1.2441261107661599E-7</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="14">
         <v>1.1969999999999999E-7</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="12">
         <f t="shared" ref="D24:D26" si="6">((B24-C24)/C24)*100</f>
         <v>3.9370184432882196</v>
       </c>
       <c r="F24" s="1">
         <v>0.01</v>
       </c>
-      <c r="G24" s="12">
-        <v>0</v>
-      </c>
-      <c r="H24" s="16">
-        <v>0</v>
-      </c>
-      <c r="I24" s="14">
+      <c r="G24" s="10">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>0</v>
+      </c>
+      <c r="I24" s="12">
         <f>IFERROR((((G24-H24)/H24)*100), 0)</f>
         <v>0</v>
       </c>
       <c r="K24" s="1">
         <v>0.01</v>
       </c>
-      <c r="L24" s="12">
+      <c r="L24" s="10">
         <v>1.1271571429460701E-6</v>
       </c>
-      <c r="M24" s="16">
+      <c r="M24" s="14">
         <v>1.124E-6</v>
       </c>
-      <c r="N24" s="14">
+      <c r="N24" s="12">
         <f t="shared" ref="N24:N26" si="7">((L24-M24)/M24)*100</f>
         <v>0.28088460374289581</v>
       </c>
@@ -4364,39 +4357,39 @@
       <c r="A25" s="1">
         <v>0.1</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="10">
         <v>1.0508192656912999E-2</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="14">
         <v>1.044E-2</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="12">
         <f t="shared" si="6"/>
         <v>0.6531863688984636</v>
       </c>
       <c r="F25" s="1">
         <v>0.1</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="10">
         <v>7.5344152155705897E-5</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="14">
         <v>7.5339999999999994E-5</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="12">
         <f t="shared" ref="I25:I26" si="8">((G25-H25)/H25)*100</f>
         <v>5.5112233951470514E-3</v>
       </c>
       <c r="K25" s="1">
         <v>0.1</v>
       </c>
-      <c r="L25" s="12">
+      <c r="L25" s="10">
         <v>1.8106627883372198E-2</v>
       </c>
-      <c r="M25" s="16">
+      <c r="M25" s="14">
         <v>1.813E-2</v>
       </c>
-      <c r="N25" s="14">
+      <c r="N25" s="12">
         <f t="shared" si="7"/>
         <v>-0.12891404648539348</v>
       </c>
@@ -4405,39 +4398,39 @@
       <c r="A26" s="1">
         <v>1</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="10">
         <v>9.5661221374500997E-3</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="14">
         <v>9.7260000000000003E-3</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="12">
         <f t="shared" si="6"/>
         <v>-1.6438192735955228</v>
       </c>
       <c r="F26" s="1">
         <v>1</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="10">
         <v>2.7230902260649999E-4</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="14">
         <v>2.7389999999999999E-4</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="12">
         <f t="shared" si="8"/>
         <v>-0.58086067670682739</v>
       </c>
       <c r="K26" s="1">
         <v>1</v>
       </c>
-      <c r="L26" s="12">
+      <c r="L26" s="10">
         <v>1.46004263748986E-2</v>
       </c>
-      <c r="M26" s="16">
+      <c r="M26" s="14">
         <v>1.465E-2</v>
       </c>
-      <c r="N26" s="14">
+      <c r="N26" s="12">
         <f t="shared" si="7"/>
         <v>-0.33838651946348214</v>
       </c>
@@ -4446,169 +4439,169 @@
       <c r="A27" s="1">
         <v>10</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="10">
         <v>5.5527106578825997E-3</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="14">
         <v>5.6979999999999999E-3</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="12">
         <f>((B27-C27)/C27)*100</f>
         <v>-2.5498305039908775</v>
       </c>
       <c r="F27" s="1">
         <v>10</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="10">
         <v>3.6715148959679997E-4</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="14">
         <v>3.6630000000000001E-4</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="12">
         <f>((G27-H27)/H27)*100</f>
         <v>0.23245689238328149</v>
       </c>
       <c r="K27" s="1">
         <v>10</v>
       </c>
-      <c r="L27" s="12">
+      <c r="L27" s="10">
         <v>8.2410990080537001E-3</v>
       </c>
-      <c r="M27" s="16">
+      <c r="M27" s="14">
         <v>8.267E-3</v>
       </c>
-      <c r="N27" s="14">
+      <c r="N27" s="12">
         <f>((L27-M27)/M27)*100</f>
         <v>-0.31330581766420684</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="14"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="14"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="14"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="12"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="12"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="12"/>
       <c r="F29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="12"/>
       <c r="K29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="12"/>
+      <c r="F30" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="14"/>
-      <c r="F30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="14"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="12"/>
       <c r="K30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="12"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>6</v>
-      </c>
       <c r="F31" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G31" s="12" t="s">
+      <c r="G31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H31" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" s="14" t="s">
-        <v>6</v>
-      </c>
       <c r="K31" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L31" s="12" t="s">
+      <c r="L31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N31" s="12" t="s">
         <v>5</v>
-      </c>
-      <c r="M31" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="N31" s="14" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>0.01</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="10">
         <v>6.3390322195127397E-8</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="14">
         <v>6.102E-8</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="12">
         <f t="shared" ref="D32:D34" si="9">((B32-C32)/C32)*100</f>
         <v>3.8845004836568298</v>
       </c>
       <c r="F32" s="1">
         <v>0.01</v>
       </c>
-      <c r="G32" s="12">
-        <v>0</v>
-      </c>
-      <c r="H32" s="16">
-        <v>0</v>
-      </c>
-      <c r="I32" s="14">
+      <c r="G32" s="10">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>0</v>
+      </c>
+      <c r="I32" s="12">
         <f>IFERROR((((G32-H32)/H32)*100), 0)</f>
         <v>0</v>
       </c>
       <c r="K32" s="1">
         <v>0.01</v>
       </c>
-      <c r="L32" s="12">
+      <c r="L32" s="10">
         <v>2.3393833392921001E-3</v>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="14">
         <v>2.3140000000000001E-3</v>
       </c>
-      <c r="N32" s="14">
+      <c r="N32" s="12">
         <f t="shared" ref="N32:N34" si="10">((L32-M32)/M32)*100</f>
         <v>1.0969463825453747</v>
       </c>
@@ -4617,39 +4610,39 @@
       <c r="A33" s="1">
         <v>0.1</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="10">
         <v>6.828303985408E-3</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="14">
         <v>6.901E-3</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="12">
         <f t="shared" si="9"/>
         <v>-1.0534127603535728</v>
       </c>
       <c r="F33" s="1">
         <v>0.1</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="10">
         <v>3.2536069815134998E-3</v>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="14">
         <v>3.2330000000000002E-3</v>
       </c>
-      <c r="I33" s="14">
+      <c r="I33" s="12">
         <f t="shared" ref="I33:I34" si="11">((G33-H33)/H33)*100</f>
         <v>0.63739503598823544</v>
       </c>
       <c r="K33" s="1">
         <v>0.1</v>
       </c>
-      <c r="L33" s="12">
+      <c r="L33" s="10">
         <v>5.1760395538698002E-3</v>
       </c>
-      <c r="M33" s="16">
+      <c r="M33" s="14">
         <v>5.1900000000000002E-3</v>
       </c>
-      <c r="N33" s="14">
+      <c r="N33" s="12">
         <f t="shared" si="10"/>
         <v>-0.26898740135260085</v>
       </c>
@@ -4658,39 +4651,39 @@
       <c r="A34" s="1">
         <v>1</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="10">
         <v>4.7378690708421E-3</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="14">
         <v>4.9220000000000002E-3</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="12">
         <f t="shared" si="9"/>
         <v>-3.7409778374217826</v>
       </c>
       <c r="F34" s="1">
         <v>1</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="10">
         <v>4.4593282159926997E-3</v>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="14">
         <v>4.4850000000000003E-3</v>
       </c>
-      <c r="I34" s="14">
+      <c r="I34" s="12">
         <f t="shared" si="11"/>
         <v>-0.57239206259310138</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
-      <c r="L34" s="12">
+      <c r="L34" s="10">
         <v>4.8405673621129E-3</v>
       </c>
-      <c r="M34" s="16">
+      <c r="M34" s="14">
         <v>4.849E-3</v>
       </c>
-      <c r="N34" s="14">
+      <c r="N34" s="12">
         <f t="shared" si="10"/>
         <v>-0.17390467904928789</v>
       </c>
@@ -4699,39 +4692,39 @@
       <c r="A35" s="1">
         <v>10</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="10">
         <v>2.8630043833568E-3</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="14">
         <v>2.98E-3</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="12">
         <f>((B35-C35)/C35)*100</f>
         <v>-3.9260274041342282</v>
       </c>
       <c r="F35" s="1">
         <v>10</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="10">
         <v>3.163474323893E-3</v>
       </c>
-      <c r="H35" s="16">
+      <c r="H35" s="14">
         <v>3.1649999999999998E-3</v>
       </c>
-      <c r="I35" s="14">
+      <c r="I35" s="12">
         <f>((G35-H35)/H35)*100</f>
         <v>-4.8204616334908815E-2</v>
       </c>
       <c r="K35" s="1">
         <v>10</v>
       </c>
-      <c r="L35" s="12">
+      <c r="L35" s="10">
         <v>2.5516063381138001E-3</v>
       </c>
-      <c r="M35" s="16">
+      <c r="M35" s="14">
         <v>2.5639999999999999E-3</v>
       </c>
-      <c r="N35" s="14">
+      <c r="N35" s="12">
         <f>((L35-M35)/M35)*100</f>
         <v>-0.48337214844772997</v>
       </c>
@@ -4740,54 +4733,54 @@
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
-      <c r="D36" s="10"/>
+      <c r="D36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="10"/>
+      <c r="I36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
-      <c r="N36" s="10"/>
+      <c r="N36" s="1"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
-      <c r="D37" s="10"/>
+      <c r="D37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="10"/>
+      <c r="I37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
-      <c r="N37" s="10"/>
+      <c r="N37" s="1"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
-      <c r="D38" s="10"/>
+      <c r="D38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="10"/>
+      <c r="I38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
-      <c r="N38" s="10"/>
+      <c r="N38" s="1"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="10"/>
+      <c r="D39" s="1"/>
       <c r="F39" s="1"/>
       <c r="H39" s="1"/>
-      <c r="I39" s="10"/>
+      <c r="I39" s="1"/>
       <c r="K39" s="1"/>
       <c r="M39" s="1"/>
-      <c r="N39" s="10"/>
+      <c r="N39" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
